--- a/order_forms/036_sound_cable_routing_request_form--order_forms.xlsx
+++ b/order_forms/036_sound_cable_routing_request_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'balanced_xlr'}</t>
+          <t>balanced_xlr</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Balanced XLR'}</t>
+          <t>Balanced XLR</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'unbalanced_xlr'}</t>
+          <t>unbalanced_xlr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Unbalanced XLR'}</t>
+          <t>Unbalanced XLR</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'optical'}</t>
+          <t>optical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Optical'}</t>
+          <t>Optical</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'soundboard1'}</t>
+          <t>soundboard1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Soundboard1'}</t>
+          <t>Soundboard1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'soundboard2'}</t>
+          <t>soundboard2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Soundboard2'}</t>
+          <t>Soundboard2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'studio_a'}</t>
+          <t>studio_a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Studio A'}</t>
+          <t>Studio A</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'studio_b'}</t>
+          <t>studio_b</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Studio B'}</t>
+          <t>Studio B</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'studio_c'}</t>
+          <t>studio_c</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Studio C'}</t>
+          <t>Studio C</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'balanced_xlr'}</t>
+          <t>balanced_xlr</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Balanced XLR'}</t>
+          <t>Balanced XLR</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'unbalanced_xlr'}</t>
+          <t>unbalanced_xlr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Unbalanced XLR'}</t>
+          <t>Unbalanced XLR</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'copper'}</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Copper'}</t>
+          <t>Copper</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'fibre'}</t>
+          <t>fibre</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Fibre'}</t>
+          <t>Fibre</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'heavy'}</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Heavy'}</t>
+          <t>Heavy</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'pvc'}</t>
+          <t>pvc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'PVC'}</t>
+          <t>PVC</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'mylar'}</t>
+          <t>mylar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Mylar'}</t>
+          <t>Mylar</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'meter'}</t>
+          <t>meter</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Meter'}</t>
+          <t>Meter</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'foot'}</t>
+          <t>foot</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Foot'}</t>
+          <t>Foot</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'copper'}</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Copper'}</t>
+          <t>Copper</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'fibre'}</t>
+          <t>fibre</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Fibre'}</t>
+          <t>Fibre</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'pvc'}</t>
+          <t>pvc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'PVC'}</t>
+          <t>PVC</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'mylar'}</t>
+          <t>mylar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Mylar'}</t>
+          <t>Mylar</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'heavy'}</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Heavy'}</t>
+          <t>Heavy</t>
         </is>
       </c>
     </row>
